--- a/Outputs/Recycling_Plot_Data/ACCII/09_Demand_vs_Availability_2050_data_ACCII.xlsx
+++ b/Outputs/Recycling_Plot_Data/ACCII/09_Demand_vs_Availability_2050_data_ACCII.xlsx
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="G14">
-        <v>0.1429080116561202</v>
+        <v>0.1427109124382286</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="G15">
-        <v>0.9019598513018334</v>
+        <v>0.9009518568937948</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="G16">
-        <v>1.95913255132475</v>
+        <v>1.956857173194804</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="G17">
-        <v>0.204895098117361</v>
+        <v>0.2046522064469845</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="G18">
-        <v>0.09537808252024788</v>
+        <v>0.09524827484585104</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="G19">
-        <v>0.8902363759751604</v>
+        <v>0.8890199809646048</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G20">
-        <v>0.0006566219024415143</v>
+        <v>0.0006576561925764655</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="G21">
-        <v>0.01348223214800244</v>
+        <v>0.01348223199349235</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="G22">
-        <v>0.003729762395465224</v>
+        <v>0.00373564213598192</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="G23">
-        <v>0.07663470449161749</v>
+        <v>0.0766347041121629</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         </is>
       </c>
       <c r="G24">
-        <v>0.00770557864255019</v>
+        <v>0.007717733465128191</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="G26">
-        <v>0.0007240178847381604</v>
+        <v>0.0007251590477603212</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="G27">
-        <v>0.01487396355243686</v>
+        <v>0.01487396345705155</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="G28">
-        <v>0.0004084431270601709</v>
+        <v>0.0004090861398647218</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="G29">
-        <v>0.008382520653617396</v>
+        <v>0.008382520520276176</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="G30">
-        <v>0.003803791915589196</v>
+        <v>0.003809786005581028</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="G31">
-        <v>0.07812966406579969</v>
+        <v>0.07812966343125505</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="G32">
-        <v>0.0004679075856823157</v>
+        <v>0.0004685979480816249</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="G33">
-        <v>0.009617773681383094</v>
+        <v>0.009616796576761124</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="G34">
-        <v>0.00231462577438464</v>
+        <v>0.002318064455510953</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="G35">
-        <v>0.04757992518460384</v>
+        <v>0.04757557084655627</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="G36">
-        <v>0.004920037454583251</v>
+        <v>0.004927342908098951</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="G37">
-        <v>0.1011438494717539</v>
+        <v>0.1011345014742037</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="G38">
-        <v>0.0004685997047099774</v>
+        <v>0.0004692949229711689</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="G39">
-        <v>0.009632481638894557</v>
+        <v>0.009631580910309148</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="G40">
-        <v>0.000292006703234101</v>
+        <v>0.0002924389716341644</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="G41">
-        <v>0.006001856621848931</v>
+        <v>0.006001276835659067</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="G42">
-        <v>0.002728296433079431</v>
+        <v>0.002732335963470044</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="G43">
-        <v>0.05608190522843469</v>
+        <v>0.05607649401825723</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="G44">
-        <v>0.003828687874441665</v>
+        <v>0.003826774500199089</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="G45">
-        <v>0.07864445797539056</v>
+        <v>0.07848134381706845</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="G46">
-        <v>0.02239803792926726</v>
+        <v>0.02239630572026801</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="G47">
-        <v>0.4602914723938597</v>
+        <v>0.4595310374068225</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         </is>
       </c>
       <c r="G48">
-        <v>0.04605946418237848</v>
+        <v>0.04605272043394042</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="G49">
-        <v>0.9468691153300856</v>
+        <v>0.9452394545064013</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="G50">
-        <v>0.004314348273322386</v>
+        <v>0.004313538893241777</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="G51">
-        <v>0.08865290380669662</v>
+        <v>0.08849668029201831</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="G52">
-        <v>0.002386607857855259</v>
+        <v>0.002385673288516427</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="G53">
-        <v>0.04900760461333409</v>
+        <v>0.04891125396607506</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="G54">
-        <v>0.02222742558681088</v>
+        <v>0.02221689117204951</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="G55">
-        <v>0.4566785526072399</v>
+        <v>0.4557431690422357</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
